--- a/backend/data/financials_by_company/1220.HK.xlsx
+++ b/backend/data/financials_by_company/1220.HK.xlsx
@@ -652,55 +652,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>-7256520</v>
+        <v>-1077170.164191</v>
       </c>
       <c r="C2" t="n">
-        <v>0.12</v>
+        <v>0.028647</v>
       </c>
       <c r="D2" t="n">
-        <v>-22542000</v>
+        <v>7392000</v>
       </c>
       <c r="E2" t="n">
-        <v>-60471000</v>
+        <v>-37601000</v>
       </c>
       <c r="F2" t="n">
-        <v>-60471000</v>
+        <v>-37601000</v>
       </c>
       <c r="G2" t="n">
-        <v>-85461000</v>
+        <v>-24910000</v>
       </c>
       <c r="H2" t="n">
-        <v>762000</v>
+        <v>1076000</v>
       </c>
       <c r="I2" t="n">
-        <v>94271000</v>
+        <v>156038000</v>
       </c>
       <c r="J2" t="n">
-        <v>-83013000</v>
+        <v>-30209000</v>
       </c>
       <c r="K2" t="n">
-        <v>-83775000</v>
+        <v>-31285000</v>
       </c>
       <c r="L2" t="n">
-        <v>-141000</v>
+        <v>-178000</v>
       </c>
       <c r="M2" t="n">
-        <v>649000</v>
+        <v>690000</v>
       </c>
       <c r="N2" t="n">
-        <v>508000</v>
+        <v>512000</v>
       </c>
       <c r="O2" t="n">
-        <v>-32246520</v>
+        <v>11613829.835809</v>
       </c>
       <c r="P2" t="n">
-        <v>-85461000</v>
+        <v>-24910000</v>
       </c>
       <c r="Q2" t="n">
-        <v>108369000</v>
+        <v>173447000</v>
       </c>
       <c r="R2" t="n">
         <v>1980000000</v>
@@ -709,85 +709,85 @@
         <v>1980000000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0432</v>
+        <v>-0.0126</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0432</v>
+        <v>-0.0126</v>
       </c>
       <c r="V2" t="n">
-        <v>-85461000</v>
+        <v>-24910000</v>
       </c>
       <c r="W2" t="n">
-        <v>-85461000</v>
+        <v>-24910000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-85461000</v>
+        <v>-24910000</v>
       </c>
       <c r="Z2" t="n">
-        <v>220000</v>
+        <v>6149000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-85681000</v>
+        <v>-31059000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-85681000</v>
+        <v>-31059000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1257000</v>
+        <v>-916000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-84424000</v>
+        <v>-31975000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2000</v>
+        <v>300000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-59619000</v>
+        <v>-34277000</v>
       </c>
       <c r="AG2" t="n">
-        <v>129000</v>
+        <v>-726000</v>
       </c>
       <c r="AH2" t="n">
-        <v>57382000</v>
+        <v>35003000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2108000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-141000</v>
+        <v>-178000</v>
       </c>
       <c r="AK2" t="n">
-        <v>649000</v>
+        <v>690000</v>
       </c>
       <c r="AL2" t="n">
-        <v>508000</v>
+        <v>512000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-23814000</v>
+        <v>4205000</v>
       </c>
       <c r="AN2" t="n">
-        <v>14098000</v>
+        <v>17409000</v>
       </c>
       <c r="AO2" t="n">
-        <v>14098000</v>
+        <v>17603000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14098000</v>
+        <v>17603000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-9716000</v>
+        <v>21614000</v>
       </c>
       <c r="AR2" t="n">
-        <v>94271000</v>
+        <v>156038000</v>
       </c>
       <c r="AS2" t="n">
-        <v>84555000</v>
+        <v>177652000</v>
       </c>
       <c r="AT2" t="n">
-        <v>84555000</v>
+        <v>177652000</v>
       </c>
     </row>
     <row r="3">
@@ -932,55 +932,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>-1077170.164191</v>
+        <v>-7256520</v>
       </c>
       <c r="C4" t="n">
-        <v>0.028647</v>
+        <v>0.12</v>
       </c>
       <c r="D4" t="n">
-        <v>7392000</v>
+        <v>-22542000</v>
       </c>
       <c r="E4" t="n">
-        <v>-37601000</v>
+        <v>-60471000</v>
       </c>
       <c r="F4" t="n">
-        <v>-37601000</v>
+        <v>-60471000</v>
       </c>
       <c r="G4" t="n">
-        <v>-24910000</v>
+        <v>-85461000</v>
       </c>
       <c r="H4" t="n">
-        <v>1076000</v>
+        <v>762000</v>
       </c>
       <c r="I4" t="n">
-        <v>156038000</v>
+        <v>94271000</v>
       </c>
       <c r="J4" t="n">
-        <v>-30209000</v>
+        <v>-83013000</v>
       </c>
       <c r="K4" t="n">
-        <v>-31285000</v>
+        <v>-83775000</v>
       </c>
       <c r="L4" t="n">
-        <v>-178000</v>
+        <v>-141000</v>
       </c>
       <c r="M4" t="n">
-        <v>690000</v>
+        <v>649000</v>
       </c>
       <c r="N4" t="n">
-        <v>512000</v>
+        <v>508000</v>
       </c>
       <c r="O4" t="n">
-        <v>11613829.835809</v>
+        <v>-32246520</v>
       </c>
       <c r="P4" t="n">
-        <v>-24910000</v>
+        <v>-85461000</v>
       </c>
       <c r="Q4" t="n">
-        <v>173447000</v>
+        <v>108369000</v>
       </c>
       <c r="R4" t="n">
         <v>1980000000</v>
@@ -989,85 +989,85 @@
         <v>1980000000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0126</v>
+        <v>-0.0432</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0126</v>
+        <v>-0.0432</v>
       </c>
       <c r="V4" t="n">
-        <v>-24910000</v>
+        <v>-85461000</v>
       </c>
       <c r="W4" t="n">
-        <v>-24910000</v>
+        <v>-85461000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-24910000</v>
+        <v>-85461000</v>
       </c>
       <c r="Z4" t="n">
-        <v>6149000</v>
+        <v>220000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-31059000</v>
+        <v>-85681000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-31059000</v>
+        <v>-85681000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-916000</v>
+        <v>1257000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-31975000</v>
+        <v>-84424000</v>
       </c>
       <c r="AE4" t="n">
-        <v>300000</v>
+        <v>2000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-34277000</v>
+        <v>-59619000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-726000</v>
+        <v>129000</v>
       </c>
       <c r="AH4" t="n">
-        <v>35003000</v>
+        <v>57382000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2108000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-178000</v>
+        <v>-141000</v>
       </c>
       <c r="AK4" t="n">
-        <v>690000</v>
+        <v>649000</v>
       </c>
       <c r="AL4" t="n">
-        <v>512000</v>
+        <v>508000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4205000</v>
+        <v>-23814000</v>
       </c>
       <c r="AN4" t="n">
-        <v>17409000</v>
+        <v>14098000</v>
       </c>
       <c r="AO4" t="n">
-        <v>17603000</v>
+        <v>14098000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17603000</v>
+        <v>14098000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21614000</v>
+        <v>-9716000</v>
       </c>
       <c r="AR4" t="n">
-        <v>156038000</v>
+        <v>94271000</v>
       </c>
       <c r="AS4" t="n">
-        <v>177652000</v>
+        <v>84555000</v>
       </c>
       <c r="AT4" t="n">
-        <v>177652000</v>
+        <v>84555000</v>
       </c>
     </row>
   </sheetData>
@@ -1368,55 +1368,51 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>44651</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1980000000</v>
       </c>
       <c r="D2" t="n">
         <v>1980000000</v>
       </c>
-      <c r="E2" t="n">
-        <v>7563000</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>12115000</v>
+        <v>16262000</v>
       </c>
       <c r="G2" t="n">
-        <v>204116000</v>
+        <v>308654000</v>
       </c>
       <c r="H2" t="n">
-        <v>216106000</v>
+        <v>324660000</v>
       </c>
       <c r="I2" t="n">
-        <v>154061000</v>
+        <v>249739000</v>
       </c>
       <c r="J2" t="n">
-        <v>204116000</v>
+        <v>308654000</v>
       </c>
       <c r="K2" t="n">
-        <v>125000</v>
+        <v>256000</v>
       </c>
       <c r="L2" t="n">
-        <v>204116000</v>
+        <v>308654000</v>
       </c>
       <c r="M2" t="n">
-        <v>206971000</v>
+        <v>315868000</v>
       </c>
       <c r="N2" t="n">
-        <v>192859000</v>
+        <v>297773000</v>
       </c>
       <c r="O2" t="n">
-        <v>-11257000</v>
+        <v>-10881000</v>
       </c>
       <c r="P2" t="n">
-        <v>204116000</v>
+        <v>308654000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-269428000</v>
+        <v>-171220000</v>
       </c>
       <c r="R2" t="n">
         <v>485679000</v>
@@ -1428,74 +1424,76 @@
         <v>19800000</v>
       </c>
       <c r="U2" t="n">
-        <v>115613000</v>
+        <v>147734000</v>
       </c>
       <c r="V2" t="n">
-        <v>2898000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>7220000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>19170000</v>
+      </c>
       <c r="X2" t="n">
-        <v>2898000</v>
+        <v>7220000</v>
       </c>
       <c r="Y2" t="n">
-        <v>43000</v>
+        <v>6000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2855000</v>
+        <v>7214000</v>
       </c>
       <c r="AA2" t="n">
-        <v>112715000</v>
+        <v>140514000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9217000</v>
+        <v>9042000</v>
       </c>
       <c r="AC2" t="n">
-        <v>82000</v>
+        <v>250000</v>
       </c>
       <c r="AD2" t="n">
-        <v>9135000</v>
+        <v>8792000</v>
       </c>
       <c r="AE2" t="n">
-        <v>102118000</v>
+        <v>39374000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9200000</v>
+        <v>6507000</v>
       </c>
       <c r="AG2" t="n">
-        <v>906000</v>
+        <v>3959000</v>
       </c>
       <c r="AH2" t="n">
-        <v>92012000</v>
+        <v>28908000</v>
       </c>
       <c r="AI2" t="n">
-        <v>308472000</v>
+        <v>445507000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>41696000</v>
+        <v>55254000</v>
       </c>
       <c r="AK2" t="n">
-        <v>6599000</v>
+        <v>8203000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6536000</v>
+        <v>11749000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6536000</v>
+        <v>11749000</v>
       </c>
       <c r="AN2" t="n">
-        <v>10443000</v>
+        <v>14473000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-6516000</v>
+        <v>-2889000</v>
       </c>
       <c r="AP2" t="n">
-        <v>16959000</v>
+        <v>17362000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>120000</v>
+        <v>246000</v>
       </c>
       <c r="AR2" t="n">
-        <v>161000</v>
+        <v>438000</v>
       </c>
       <c r="AS2" t="n">
         <v>16678000</v>
@@ -1504,33 +1502,37 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>266776000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>390253000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>18000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>21608000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>28431000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>186096000</v>
+      </c>
       <c r="AY2" t="n">
-        <v>65519000</v>
+        <v>260167000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-47804000</v>
+        <v>-20118000</v>
       </c>
       <c r="BA2" t="n">
-        <v>176525000</v>
+        <v>34531000</v>
       </c>
       <c r="BB2" t="n">
-        <v>14273000</v>
+        <v>87242000</v>
       </c>
       <c r="BC2" t="n">
-        <v>9846000</v>
+        <v>24824000</v>
       </c>
       <c r="BD2" t="n">
-        <v>4427000</v>
+        <v>62418000</v>
       </c>
       <c r="BE2" t="n">
-        <v>4427000</v>
+        <v>62418000</v>
       </c>
     </row>
     <row r="3">
@@ -1700,51 +1702,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45382</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>1980000000</v>
       </c>
       <c r="D4" t="n">
         <v>1980000000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>7563000</v>
+      </c>
       <c r="F4" t="n">
-        <v>16262000</v>
+        <v>12115000</v>
       </c>
       <c r="G4" t="n">
-        <v>308654000</v>
+        <v>204116000</v>
       </c>
       <c r="H4" t="n">
-        <v>324660000</v>
+        <v>216106000</v>
       </c>
       <c r="I4" t="n">
-        <v>249739000</v>
+        <v>154061000</v>
       </c>
       <c r="J4" t="n">
-        <v>308654000</v>
+        <v>204116000</v>
       </c>
       <c r="K4" t="n">
-        <v>256000</v>
+        <v>125000</v>
       </c>
       <c r="L4" t="n">
-        <v>308654000</v>
+        <v>204116000</v>
       </c>
       <c r="M4" t="n">
-        <v>315868000</v>
+        <v>206971000</v>
       </c>
       <c r="N4" t="n">
-        <v>297773000</v>
+        <v>192859000</v>
       </c>
       <c r="O4" t="n">
-        <v>-10881000</v>
+        <v>-11257000</v>
       </c>
       <c r="P4" t="n">
-        <v>308654000</v>
+        <v>204116000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-171220000</v>
+        <v>-269428000</v>
       </c>
       <c r="R4" t="n">
         <v>485679000</v>
@@ -1756,76 +1762,74 @@
         <v>19800000</v>
       </c>
       <c r="U4" t="n">
-        <v>147734000</v>
+        <v>115613000</v>
       </c>
       <c r="V4" t="n">
-        <v>7220000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19170000</v>
-      </c>
+        <v>2898000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>7220000</v>
+        <v>2898000</v>
       </c>
       <c r="Y4" t="n">
-        <v>6000</v>
+        <v>43000</v>
       </c>
       <c r="Z4" t="n">
-        <v>7214000</v>
+        <v>2855000</v>
       </c>
       <c r="AA4" t="n">
-        <v>140514000</v>
+        <v>112715000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9042000</v>
+        <v>9217000</v>
       </c>
       <c r="AC4" t="n">
-        <v>250000</v>
+        <v>82000</v>
       </c>
       <c r="AD4" t="n">
-        <v>8792000</v>
+        <v>9135000</v>
       </c>
       <c r="AE4" t="n">
-        <v>39374000</v>
+        <v>102118000</v>
       </c>
       <c r="AF4" t="n">
-        <v>6507000</v>
+        <v>9200000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3959000</v>
+        <v>906000</v>
       </c>
       <c r="AH4" t="n">
-        <v>28908000</v>
+        <v>92012000</v>
       </c>
       <c r="AI4" t="n">
-        <v>445507000</v>
+        <v>308472000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55254000</v>
+        <v>41696000</v>
       </c>
       <c r="AK4" t="n">
-        <v>8203000</v>
+        <v>6599000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11749000</v>
+        <v>6536000</v>
       </c>
       <c r="AM4" t="n">
-        <v>11749000</v>
+        <v>6536000</v>
       </c>
       <c r="AN4" t="n">
-        <v>14473000</v>
+        <v>10443000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-2889000</v>
+        <v>-6516000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17362000</v>
+        <v>16959000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>246000</v>
+        <v>120000</v>
       </c>
       <c r="AR4" t="n">
-        <v>438000</v>
+        <v>161000</v>
       </c>
       <c r="AS4" t="n">
         <v>16678000</v>
@@ -1834,37 +1838,33 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>390253000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>18000</v>
-      </c>
+        <v>266776000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>28431000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>186096000</v>
-      </c>
+        <v>21608000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>260167000</v>
+        <v>65519000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-20118000</v>
+        <v>-47804000</v>
       </c>
       <c r="BA4" t="n">
-        <v>34531000</v>
+        <v>176525000</v>
       </c>
       <c r="BB4" t="n">
-        <v>87242000</v>
+        <v>14273000</v>
       </c>
       <c r="BC4" t="n">
-        <v>24824000</v>
+        <v>9846000</v>
       </c>
       <c r="BD4" t="n">
-        <v>62418000</v>
+        <v>4427000</v>
       </c>
       <c r="BE4" t="n">
-        <v>62418000</v>
+        <v>4427000</v>
       </c>
     </row>
   </sheetData>
@@ -2060,106 +2060,110 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>-14210000</v>
+        <v>-23384000</v>
       </c>
       <c r="C2" t="n">
-        <v>-2017000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>-4118000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-30000</v>
+      </c>
       <c r="E2" t="n">
-        <v>2483000</v>
+        <v>60656000</v>
       </c>
       <c r="F2" t="n">
-        <v>19004000</v>
+        <v>88842000</v>
       </c>
       <c r="G2" t="n">
-        <v>8000</v>
+        <v>-101000</v>
       </c>
       <c r="H2" t="n">
-        <v>-16529000</v>
+        <v>-28085000</v>
       </c>
       <c r="I2" t="n">
-        <v>-2768000</v>
+        <v>-5273000</v>
       </c>
       <c r="J2" t="n">
-        <v>-523000</v>
+        <v>-690000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2017000</v>
+        <v>-4118000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2017000</v>
+        <v>-4118000</v>
       </c>
       <c r="M2" t="n">
-        <v>-2017000</v>
+        <v>-4118000</v>
       </c>
       <c r="N2" t="n">
-        <v>449000</v>
+        <v>542000</v>
       </c>
       <c r="O2" t="n">
-        <v>-59000</v>
+        <v>-1239000</v>
       </c>
       <c r="P2" t="n">
-        <v>508000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>512000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1299000</v>
+      </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="U2" t="n">
-        <v>-14210000</v>
+        <v>-23354000</v>
       </c>
       <c r="V2" t="n">
-        <v>-639000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-126000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>9607000</v>
+        <v>-28635000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-63792000</v>
+        <v>43620000</v>
       </c>
       <c r="Z2" t="n">
-        <v>55567000</v>
+        <v>-13467000</v>
       </c>
       <c r="AA2" t="n">
-        <v>20533000</v>
+        <v>-65383000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2701000</v>
+        <v>6595000</v>
       </c>
       <c r="AC2" t="n">
-        <v>139000</v>
+        <v>-122000</v>
       </c>
       <c r="AD2" t="n">
-        <v>762000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>1076000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="n">
-        <v>762000</v>
+        <v>1076000</v>
       </c>
       <c r="AG2" t="n">
-        <v>852000</v>
+        <v>2025000</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>129000</v>
+        <v>-726000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-84424000</v>
+        <v>-31975000</v>
       </c>
     </row>
     <row r="3">
@@ -2272,110 +2276,106 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>-23384000</v>
+        <v>-14210000</v>
       </c>
       <c r="C4" t="n">
-        <v>-4118000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-30000</v>
-      </c>
+        <v>-2017000</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>60656000</v>
+        <v>2483000</v>
       </c>
       <c r="F4" t="n">
-        <v>88842000</v>
+        <v>19004000</v>
       </c>
       <c r="G4" t="n">
-        <v>-101000</v>
+        <v>8000</v>
       </c>
       <c r="H4" t="n">
-        <v>-28085000</v>
+        <v>-16529000</v>
       </c>
       <c r="I4" t="n">
-        <v>-5273000</v>
+        <v>-2768000</v>
       </c>
       <c r="J4" t="n">
-        <v>-690000</v>
+        <v>-523000</v>
       </c>
       <c r="K4" t="n">
-        <v>-4118000</v>
+        <v>-2017000</v>
       </c>
       <c r="L4" t="n">
-        <v>-4118000</v>
+        <v>-2017000</v>
       </c>
       <c r="M4" t="n">
-        <v>-4118000</v>
+        <v>-2017000</v>
       </c>
       <c r="N4" t="n">
-        <v>542000</v>
+        <v>449000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1239000</v>
+        <v>-59000</v>
       </c>
       <c r="P4" t="n">
-        <v>512000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1299000</v>
-      </c>
+        <v>508000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-23354000</v>
+        <v>-14210000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>-639000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-126000</v>
+      </c>
       <c r="X4" t="n">
-        <v>-28635000</v>
+        <v>9607000</v>
       </c>
       <c r="Y4" t="n">
-        <v>43620000</v>
+        <v>-63792000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-13467000</v>
+        <v>55567000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-65383000</v>
+        <v>20533000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6595000</v>
+        <v>-2701000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-122000</v>
+        <v>139000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1076000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
+        <v>762000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>1076000</v>
+        <v>762000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2025000</v>
+        <v>852000</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-726000</v>
+        <v>129000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-31975000</v>
+        <v>-84424000</v>
       </c>
     </row>
   </sheetData>
@@ -2880,187 +2880,187 @@
       </c>
       <c r="CT1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
@@ -3190,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.667</v>
+        <v>2.593</v>
       </c>
       <c r="AE2" t="n">
         <v>1200000</v>
@@ -3220,10 +3220,10 @@
         <v>116480000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.064</v>
+        <v>0.058</v>
       </c>
       <c r="AP2" t="n">
         <v>2.79</v>
@@ -3303,10 +3303,10 @@
         <v>-1.373</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.05084747</v>
+        <v>-0.034482777</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3413,140 +3413,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0</v>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>ZHIDAO INT'L</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Zhidao International (Holdings) Limited</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="CW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="n">
+        <v>1751270059</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>finmb_4492991</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-1.754383</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
         <v>15</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="DI2" t="n">
         <v>15</v>
       </c>
-      <c r="CZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>finmb_4492991</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Zhidao International (Holdings) Limited</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>1751270059</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>ZHIDAO INT'L</t>
-        </is>
-      </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
         <v>1039743000000</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DM2" t="n">
         <v>-0.0009999983000000001</v>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>0.051 - 0.057</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.0050000027</v>
+      </c>
       <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.006000001</v>
+        <v>0.09803927</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.051 - 0.058</t>
+        </is>
       </c>
       <c r="DT2" t="n">
-        <v>0.12000002</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>0.05 - 0.064</t>
-        </is>
+        <v>-0.0019999966</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.034482703</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.008000001</v>
+        <v>-3.4482777</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.12500001</v>
+        <v>1732873371</v>
       </c>
       <c r="DX2" t="n">
-        <v>-5.0847473</v>
-      </c>
-      <c r="DY2" t="n">
         <v>1732873371</v>
       </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
       <c r="DZ2" t="n">
-        <v>1732873371</v>
-      </c>
-      <c r="EA2" t="b">
+        <v>-0.05</v>
+      </c>
+      <c r="EA2" t="n">
         <v>0</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-1.754383</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="inlineStr"/>
     </row>
